--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="153">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:54:27+00:00</t>
+    <t>2026-01-30T10:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -384,9 +384,6 @@
 </t>
   </si>
   <si>
-    <t>publicPrisEnCharge</t>
-  </si>
-  <si>
     <t>Extension.extension:ageRange</t>
   </si>
   <si>
@@ -463,9 +460,6 @@
 qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
-    <t>ageMin</t>
-  </si>
-  <si>
     <t>./low</t>
   </si>
   <si>
@@ -485,9 +479,6 @@
   </si>
   <si>
     <t>Range.high</t>
-  </si>
-  <si>
-    <t>ageMax</t>
   </si>
   <si>
     <t>./high</t>
@@ -1804,7 +1795,7 @@
         <v>119</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>110</v>
@@ -1812,13 +1803,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -1920,7 +1911,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>100</v>
@@ -2026,7 +2017,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>102</v>
@@ -2132,7 +2123,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>104</v>
@@ -2175,7 +2166,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>76</v>
@@ -2240,7 +2231,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>112</v>
@@ -2266,7 +2257,7 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>114</v>
@@ -2346,10 +2337,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2452,14 +2443,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2481,13 +2472,13 @@
         <v>91</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2560,10 +2551,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2583,19 +2574,19 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="K17" t="s" s="2">
+      <c r="L17" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2645,7 +2636,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -2657,21 +2648,21 @@
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>146</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2691,19 +2682,19 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="K18" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="K18" t="s" s="2">
-        <v>139</v>
-      </c>
       <c r="L18" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2753,7 +2744,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -2765,13 +2756,13 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19">
@@ -2910,7 +2901,7 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>114</v>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,7 +440,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -796,43 +796,43 @@
   <dimension ref="A1:AL20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.03515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.25390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.30859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.0390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="31.94140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.4140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="95.86328125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="82.18359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="86.46875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="74.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice-patient-type.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
